--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20261022.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20261022.xlsx
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>37,190,000</t>
+          <t>30,062,899</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>30,062,899</t>
+          <t>37,190,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
